--- a/esyluban/examples/release/DataTables/test/test_desc.xlsx
+++ b/esyluban/examples/release/DataTables/test/test_desc.xlsx
@@ -725,12 +725,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I4:J4"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="I3:J3"/>
   </mergeCells>
